--- a/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onko-intention-sct.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onko-intention-sct.xlsx
@@ -51,7 +51,7 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping Intention Codes zu SNOMED-CT</t>
+    <t>Mapping Intention Codes zu SNOMED-CT STATUS DIESER ZUORDNUNG: 2024 erstellt, gegen SNOMED CT International 20240401. Sie ist WEDER OFFIZIELL ENDORSED NOCH FINAL QUALITAETSGESICHERT - es handelt sich um einen projektseitigen Arbeitsstand, nicht um eine abgestimmte Referenz. Die Zielcodes sind gegen neuere SNOMED-Releases nicht nachverifiziert; einzelne Konzepte koennen inzwischen inaktiviert oder ersetzt sein. Vor einer Nutzung in Produktivsystemen sind fachliche Pruefung und ein Abgleich gegen die eingesetzte SNOMED-Version erforderlich.</t>
   </si>
   <si>
     <t>Purpose</t>
